--- a/data/gas/processed/thermal_generation_2025.xlsx
+++ b/data/gas/processed/thermal_generation_2025.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pc\Desktop\MSc\AUST\thesis-code\data\gas\processed\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pc\Desktop\MSc\AUST\Thesis\thesis-repo\thesis-code\data\gas\processed\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FB7F7B04-6F38-4C6A-9010-581695F81343}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3F916030-2625-4F64-A501-42E6DDF1D871}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2172" yWindow="432" windowWidth="11268" windowHeight="12132" xr2:uid="{92C16D02-A4AD-4680-A825-9F62DC52AD19}"/>
+    <workbookView xWindow="10620" yWindow="180" windowWidth="11280" windowHeight="12132" xr2:uid="{92C16D02-A4AD-4680-A825-9F62DC52AD19}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet2" sheetId="2" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="181029" iterateDelta="1E-4"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="16">
   <si>
     <t>Q1</t>
   </si>
@@ -67,6 +67,12 @@
   </si>
   <si>
     <t>Thermal_generation_gwh</t>
+  </si>
+  <si>
+    <t>Q4</t>
+  </si>
+  <si>
+    <t>As at 2025/Q4, Nigeria has 28 power plants supplying to national grid. Consisting of 5 Hydro, 2 Steam, 19 Open Cycle Gas Turbines, 2 combined Cycle Gas Turbine</t>
   </si>
 </sst>
 </file>
@@ -438,7 +444,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9747CE26-BF7B-4AC2-9CB5-9D5300B2B5D5}">
-  <dimension ref="A1:G4"/>
+  <dimension ref="A1:G7"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="3" max="3" width="23.21875" bestFit="1" customWidth="1"/>
@@ -524,6 +530,22 @@
         <v>12</v>
       </c>
     </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="B5" t="s">
+        <v>14</v>
+      </c>
+      <c r="C5">
+        <v>9831.58</v>
+      </c>
+      <c r="D5">
+        <v>6065.16</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="G7" t="s">
+        <v>15</v>
+      </c>
+    </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="E3" r:id="rId1" xr:uid="{8002BB33-5BA9-4B62-8D62-1E62F56AF786}"/>

--- a/data/gas/processed/thermal_generation_2025.xlsx
+++ b/data/gas/processed/thermal_generation_2025.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pc\Desktop\MSc\AUST\Thesis\thesis-repo\thesis-code\data\gas\processed\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3F916030-2625-4F64-A501-42E6DDF1D871}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8ABAD71C-76B0-43A7-AF04-6A9B6BC555B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="10620" yWindow="180" windowWidth="11280" windowHeight="12132" xr2:uid="{92C16D02-A4AD-4680-A825-9F62DC52AD19}"/>
+    <workbookView xWindow="10980" yWindow="156" windowWidth="11724" windowHeight="12228" xr2:uid="{92C16D02-A4AD-4680-A825-9F62DC52AD19}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet2" sheetId="2" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="17">
   <si>
     <t>Q1</t>
   </si>
@@ -73,6 +73,9 @@
   </si>
   <si>
     <t>As at 2025/Q4, Nigeria has 28 power plants supplying to national grid. Consisting of 5 Hydro, 2 Steam, 19 Open Cycle Gas Turbines, 2 combined Cycle Gas Turbine</t>
+  </si>
+  <si>
+    <t>phase 5 item: Combined physical-parameter envelope run</t>
   </si>
 </sst>
 </file>
@@ -444,7 +447,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9747CE26-BF7B-4AC2-9CB5-9D5300B2B5D5}">
-  <dimension ref="A1:G7"/>
+  <dimension ref="A1:G15"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="3" max="3" width="23.21875" bestFit="1" customWidth="1"/>
@@ -487,7 +490,8 @@
         <v>10304.469999999999</v>
       </c>
       <c r="D2">
-        <v>7222.59</v>
+        <f>C2-(29.91% * C2)</f>
+        <v>7222.4030229999998</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>10</v>
@@ -504,7 +508,8 @@
         <v>9830.31</v>
       </c>
       <c r="D3">
-        <v>6863.03</v>
+        <f>C3-(30.19%*C3)</f>
+        <v>6862.5394109999997</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>9</v>
@@ -518,10 +523,11 @@
         <v>2</v>
       </c>
       <c r="C4">
-        <v>9227.57</v>
+        <v>9227.56</v>
       </c>
       <c r="D4">
-        <v>6260.88</v>
+        <f>C4-(32.43%*C4)</f>
+        <v>6235.0622920000005</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>11</v>
@@ -535,15 +541,27 @@
         <v>14</v>
       </c>
       <c r="C5">
-        <v>9831.58</v>
+        <v>9831.52</v>
       </c>
       <c r="D5">
-        <v>6065.16</v>
+        <f>C5-(38.31%*C5)</f>
+        <v>6065.0646880000004</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="D6">
+        <f>SUM(D2:D5)</f>
+        <v>26385.069413999998</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="G7" t="s">
         <v>15</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
+        <v>16</v>
       </c>
     </row>
   </sheetData>

--- a/data/gas/processed/thermal_generation_2025.xlsx
+++ b/data/gas/processed/thermal_generation_2025.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pc\Desktop\MSc\AUST\Thesis\thesis-repo\thesis-code\data\gas\processed\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8ABAD71C-76B0-43A7-AF04-6A9B6BC555B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{27EC2458-5580-45E1-A392-D029CE169676}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="10980" yWindow="156" windowWidth="11724" windowHeight="12228" xr2:uid="{92C16D02-A4AD-4680-A825-9F62DC52AD19}"/>
+    <workbookView xWindow="10980" yWindow="132" windowWidth="11724" windowHeight="12228" xr2:uid="{92C16D02-A4AD-4680-A825-9F62DC52AD19}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet2" sheetId="2" r:id="rId1"/>
@@ -447,7 +447,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9747CE26-BF7B-4AC2-9CB5-9D5300B2B5D5}">
-  <dimension ref="A1:G15"/>
+  <dimension ref="A1:G16"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="3" max="3" width="23.21875" bestFit="1" customWidth="1"/>
@@ -564,6 +564,12 @@
         <v>16</v>
       </c>
     </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A16">
+        <f>74.05%*8887.93</f>
+        <v>6581.5121650000001</v>
+      </c>
+    </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="E3" r:id="rId1" xr:uid="{8002BB33-5BA9-4B62-8D62-1E62F56AF786}"/>
